--- a/data/trans_dic/IP18A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,51</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,97</t>
+          <t>0,99; 6,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,77</t>
+          <t>0,25; 2,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,41</t>
+          <t>0,77; 3,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,6</t>
+          <t>0,23; 2,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,4</t>
+          <t>0,58; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,67</t>
+          <t>0,32; 2,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 14,17</t>
+          <t>1,73; 15,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,73</t>
+          <t>0,18; 1,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,38</t>
+          <t>0,6; 2,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,3</t>
+          <t>0,92; 10,4</t>
         </is>
       </c>
     </row>
@@ -996,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,62</t>
+          <t>0,43; 4,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,99</t>
+          <t>0,44; 3,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 16,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 7,47</t>
+          <t>1,52; 7,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 20,77</t>
+          <t>1,77; 27,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,19</t>
+          <t>0,22; 1,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,53</t>
+          <t>1,23; 4,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,34</t>
+          <t>2,18; 16,26</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,37</t>
+          <t>0,36; 3,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,7</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,64</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,69</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,28</t>
+          <t>0,38; 2,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,95</t>
+          <t>0,2; 1,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,77</t>
+          <t>0,19; 1,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 4,85</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,45</t>
+          <t>0,22; 1,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,63</t>
+          <t>0,33; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,18</t>
+          <t>0,59; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,0</t>
+          <t>0,79; 6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,4</t>
+          <t>0,22; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,87</t>
+          <t>0,6; 1,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,46</t>
+          <t>0,83; 2,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,85</t>
+          <t>1,7; 9,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,08</t>
+          <t>0,3; 1,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,51</t>
+          <t>0,63; 1,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,89</t>
+          <t>0,87; 1,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,5</t>
+          <t>1,89; 6,48</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2416</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4777</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3695</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6600</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3904</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5382</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1438; 8944</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2959</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>600; 6247</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2118; 9229</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>602; 7030</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3810</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2983</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5055</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4940</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1117; 6001</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4125</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5020</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>669; 5559</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>863; 7582</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3432</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>728; 7325</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2423; 9355</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>728; 8189</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2515</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>610; 5702</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>600; 5116</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4374</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2428</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4002</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2171; 10819</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>559; 8646</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2891</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>651; 5887</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3428; 13395</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1264; 9418</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>702; 6385</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4698</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3851</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2727</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4899</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5308</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6029</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1407; 8569</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>790; 7350</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>717; 7385</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2743</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7422</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13489</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>16946</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1320; 8076</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2190; 10369</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3753; 12783</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>797; 6287</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1380; 8572</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4266; 14013</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5530; 16171</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2233; 12147</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3656; 13131</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8696; 20149</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11414; 25473</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4383; 15019</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Habitat-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,89</t>
+          <t>0,0; 22,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,15</t>
+          <t>0,97; 5,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,56</t>
+          <t>0,3; 2,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,36</t>
+          <t>0,77; 3,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,72</t>
+          <t>0,23; 3,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,1</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,66</t>
+          <t>0,32; 2,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 15,24</t>
+          <t>1,75; 15,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,85</t>
+          <t>0,18; 1,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,33</t>
+          <t>0,65; 2,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,4</t>
+          <t>1,06; 9,78</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,01</t>
+          <t>0,43; 3,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,76</t>
+          <t>0,44; 3,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,67</t>
+          <t>0,0; 15,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,55</t>
+          <t>1,51; 7,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 27,29</t>
+          <t>1,6; 23,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,98</t>
+          <t>0,22; 2,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,8</t>
+          <t>1,15; 4,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 16,26</t>
+          <t>2,17; 16,07</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,32</t>
+          <t>0,37; 3,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,69</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,7</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,64</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,29</t>
+          <t>0,4; 2,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,21; 1,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,99</t>
+          <t>0,19; 1,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,35</t>
+          <t>0,22; 1,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,41; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,0</t>
+          <t>0,58; 2,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,27</t>
+          <t>1,15; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,37</t>
+          <t>0,19; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,98</t>
+          <t>0,58; 1,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,41</t>
+          <t>0,75; 2,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,23</t>
+          <t>1,81; 9,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,08</t>
+          <t>0,31; 1,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,47</t>
+          <t>0,62; 1,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,94</t>
+          <t>0,84; 1,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,48</t>
+          <t>1,85; 6,4</t>
         </is>
       </c>
     </row>
@@ -1645,37 +1645,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>0; 4471</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3695</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6600</t>
+          <t>0; 6172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3904</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5382</t>
+          <t>0; 5624</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1438; 8944</t>
+          <t>1406; 8631</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2959</t>
+          <t>0; 3405</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>600; 6247</t>
+          <t>721; 6645</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2118; 9229</t>
+          <t>2104; 9861</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>602; 7030</t>
+          <t>602; 8011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3810</t>
+          <t>0; 3779</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 4317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1117; 6001</t>
+          <t>1161; 6568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,42 +1873,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4125</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5020</t>
+          <t>0; 5073</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>669; 5559</t>
+          <t>675; 5615</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>863; 7582</t>
+          <t>870; 7942</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3432</t>
+          <t>0; 2965</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>728; 7325</t>
+          <t>729; 7022</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2423; 9355</t>
+          <t>2607; 10565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>728; 8189</t>
+          <t>833; 7699</t>
         </is>
       </c>
     </row>
@@ -2066,57 +2066,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>610; 5702</t>
+          <t>610; 5152</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>600; 5116</t>
+          <t>602; 5198</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4374</t>
+          <t>0; 3961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2428</t>
+          <t>0; 2559</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 3376</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2171; 10819</t>
+          <t>2167; 11270</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>559; 8646</t>
+          <t>507; 7305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2891</t>
+          <t>0; 2423</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651; 5887</t>
+          <t>654; 5950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3428; 13395</t>
+          <t>3219; 13414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1264; 9418</t>
+          <t>1259; 9306</t>
         </is>
       </c>
     </row>
@@ -2269,37 +2269,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>702; 6385</t>
+          <t>711; 6522</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4698</t>
+          <t>0; 4728</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3851</t>
+          <t>0; 4687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2727</t>
+          <t>0; 2751</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4899</t>
+          <t>0; 4885</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5308</t>
+          <t>0; 5430</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6029</t>
+          <t>0; 6464</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2309,22 +2309,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1407; 8569</t>
+          <t>1479; 8899</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>790; 7350</t>
+          <t>826; 7639</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>717; 7385</t>
+          <t>712; 7280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2743</t>
+          <t>0; 2830</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1320; 8076</t>
+          <t>1329; 8387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2190; 10369</t>
+          <t>2710; 10542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3753; 12783</t>
+          <t>3692; 13046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>797; 6287</t>
+          <t>1150; 6645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1380; 8572</t>
+          <t>1172; 8518</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4266; 14013</t>
+          <t>4112; 14009</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5530; 16171</t>
+          <t>5013; 16009</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2233; 12147</t>
+          <t>2388; 12110</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656; 13131</t>
+          <t>3832; 13324</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8696; 20149</t>
+          <t>8545; 20865</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11414; 25473</t>
+          <t>10957; 25045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4383; 15019</t>
+          <t>4295; 14847</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A05-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>1,35; 5,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,94</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,73</t>
+          <t>0,24; 2,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,59</t>
+          <t>0,77; 3,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,1</t>
+          <t>0,23; 2,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
     </row>
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,32; 2,67</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2,08; 15,41</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 3,4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,51</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,59; 3,4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,91</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,48</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 2,69</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 15,97</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,77</t>
+          <t>0,2; 1,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,63</t>
+          <t>0,59; 2,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,78</t>
+          <t>1,45; 10,96</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,82</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,34</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1,44; 7,47</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,03; 21,79</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,43; 3,63</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 3,82</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,1</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,91</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,43; 3,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,87</t>
+          <t>0,44; 3,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 23,06</t>
+          <t>0,0; 19,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,0</t>
+          <t>0,22; 2,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,8</t>
+          <t>1,23; 4,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 16,07</t>
+          <t>2,1; 16,88</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,39</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,37; 3,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,38</t>
+          <t>0,38; 2,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,9</t>
+          <t>0,2; 1,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,96</t>
+          <t>0,19; 1,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,59</t>
+          <t>0,58; 1,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,04</t>
+          <t>0,76; 2,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,62</t>
+          <t>2,0; 10,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,37</t>
+          <t>0,24; 1,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,98</t>
+          <t>0,4; 1,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,39</t>
+          <t>0,65; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,2</t>
+          <t>1,0; 7,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,09</t>
+          <t>0,31; 1,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,52</t>
+          <t>0,61; 1,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,91</t>
+          <t>0,83; 1,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,4</t>
+          <t>2,07; 6,8</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>736</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1764</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4173</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1046</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>1959; 8677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6172</t>
+          <t>0; 3280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5624</t>
+          <t>0; 4410</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1406; 8631</t>
+          <t>0; 3766</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3405</t>
+          <t>0; 6495</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3305</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721; 6645</t>
+          <t>597; 6753</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2104; 9861</t>
+          <t>2123; 9351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>602; 8011</t>
+          <t>600; 6700</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3779</t>
+          <t>0; 3873</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,49 +1785,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1401</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2983</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2861</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3088</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4972</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>670; 5567</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>946; 6997</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4317</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1161; 6568</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4802</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1150; 6565</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3433</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5073</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>675; 5615</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>870; 7942</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2965</t>
+          <t>0; 4211</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>729; 7022</t>
+          <t>781; 6829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2607; 10565</t>
+          <t>2378; 9569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>833; 7699</t>
+          <t>1048; 7930</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1917</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1903</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2591</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3644</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 2433</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3643</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2058; 10707</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>311; 6577</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>610; 5152</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>602; 5198</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3961</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2559</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>609; 5143</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2167; 11270</t>
+          <t>597; 5431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>507; 7305</t>
+          <t>0; 4723</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2423</t>
+          <t>0; 2413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>654; 5950</t>
+          <t>653; 6526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3219; 13414</t>
+          <t>3443; 12641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1259; 9306</t>
+          <t>1131; 9101</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2376</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1559</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1570</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>478</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>711; 6522</t>
+          <t>0; 4785</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4728</t>
+          <t>0; 5420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4687</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2751</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4885</t>
+          <t>712; 6491</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6464</t>
+          <t>0; 3898</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2483</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1479; 8899</t>
+          <t>1415; 8526</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>826; 7639</t>
+          <t>819; 7848</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712; 7280</t>
+          <t>707; 6558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2830</t>
+          <t>0; 2407</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1329; 8387</t>
+          <t>1386; 8710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2710; 10542</t>
+          <t>4125; 13234</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3692; 13046</t>
+          <t>5075; 16503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1150; 6645</t>
+          <t>2435; 12689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1172; 8518</t>
+          <t>1435; 8668</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4112; 14009</t>
+          <t>2631; 10814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5013; 16009</t>
+          <t>4139; 13964</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2388; 12110</t>
+          <t>952; 7018</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3832; 13324</t>
+          <t>3768; 13215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8545; 20865</t>
+          <t>8313; 20692</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10957; 25045</t>
+          <t>10889; 24821</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4295; 14847</t>
+          <t>4507; 14770</t>
         </is>
       </c>
     </row>
